--- a/ig/DM-JUILLET-2026/CodeSystem-TRE-R239-PublicPrisEnCharge.xlsx
+++ b/ig/DM-JUILLET-2026/CodeSystem-TRE-R239-PublicPrisEnCharge.xlsx
@@ -118,148 +118,148 @@
     <t>Count</t>
   </si>
   <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>01</t>
+  </si>
+  <si>
+    <t>Personnes âgées en perte d'autonomie (PA) et aidants</t>
+  </si>
+  <si>
+    <t>02</t>
+  </si>
+  <si>
+    <t>Personnes en situation de handicap (PH) et aidants</t>
+  </si>
+  <si>
+    <t>03</t>
+  </si>
+  <si>
+    <t>Personnes âgées autonomes</t>
+  </si>
+  <si>
+    <t>04</t>
+  </si>
+  <si>
+    <t>Personnes présentant une conduite addictive</t>
+  </si>
+  <si>
+    <t>05</t>
+  </si>
+  <si>
+    <t>Personnes handicapées vieillissantes</t>
+  </si>
+  <si>
+    <t>06</t>
+  </si>
+  <si>
+    <t>Personnes en situation de précarité</t>
+  </si>
+  <si>
+    <t>07</t>
+  </si>
+  <si>
+    <t>Tout public</t>
+  </si>
+  <si>
+    <t>08</t>
+  </si>
+  <si>
+    <t>Etudiants</t>
+  </si>
+  <si>
+    <t>09</t>
+  </si>
+  <si>
+    <t>Personnes atteintes de pathologies chroniques ou présentant une affection de longue durée (ALD)</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/concept-properties#dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>01</t>
-  </si>
-  <si>
-    <t>Personnes âgées en perte d'autonomie et aidants</t>
-  </si>
-  <si>
-    <t>02</t>
-  </si>
-  <si>
-    <t>Personnes en situation de handicap et aidants</t>
-  </si>
-  <si>
-    <t>03</t>
-  </si>
-  <si>
-    <t>Personnes âgées autonomes</t>
-  </si>
-  <si>
-    <t>04</t>
-  </si>
-  <si>
-    <t>Personnes présentant une conduite addictive</t>
-  </si>
-  <si>
-    <t>05</t>
-  </si>
-  <si>
-    <t>Personnes handicapées vieillissantes</t>
-  </si>
-  <si>
-    <t>06</t>
-  </si>
-  <si>
-    <t>Personnes en situation de précarité</t>
-  </si>
-  <si>
-    <t>07</t>
-  </si>
-  <si>
-    <t>Tout public</t>
-  </si>
-  <si>
-    <t>08</t>
-  </si>
-  <si>
-    <t>Etudiants</t>
-  </si>
-  <si>
-    <t>09</t>
-  </si>
-  <si>
-    <t>Personnes atteintes de pathologies chroniques ou présentant une ALD</t>
-  </si>
-  <si>
     <t>Victime de violence</t>
-  </si>
-  <si>
-    <t>11</t>
   </si>
   <si>
     <t>Auteur de violence ou à risque de violence</t>
@@ -808,10 +808,10 @@
         <v>61</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D11" s="2"/>
     </row>
@@ -820,7 +820,7 @@
         <v>61</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="C12" t="s" s="2">
         <v>82</v>
